--- a/data/trans_orig/IP07B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07B-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general autopercibida en 2007 (tasa de respuesta: 87,69%)</t>
+          <t>Menores según su salud general autopercibida en 2007 (tasa de respuesta: 87,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>1573</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>8260</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7756</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>13853</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20587</t>
+          <t>20551</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30141</t>
+          <t>29962</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17248</t>
+          <t>18154</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26184</t>
+          <t>26430</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41036</t>
+          <t>40951</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54046</t>
+          <t>53918</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,31%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12622</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10739</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20292</t>
+          <t>20137</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8760</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10164</t>
+          <t>10280</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15809</t>
+          <t>15966</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8317</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15739</t>
+          <t>16317</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13041</t>
+          <t>12608</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21482</t>
+          <t>21317</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23450</t>
+          <t>23585</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35164</t>
+          <t>34883</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,41%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10679</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>9343</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>7974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18215</t>
+          <t>17966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,17%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10926</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6184</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15449</t>
+          <t>15868</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>11924</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23620</t>
+          <t>23358</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18218</t>
+          <t>18523</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28311</t>
+          <t>28458</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38981</t>
+          <t>39153</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40967</t>
+          <t>41649</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55133</t>
+          <t>54758</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,49%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>7667</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13959</t>
+          <t>13835</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16239</t>
+          <t>17025</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29355</t>
+          <t>29889</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13098</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25199</t>
+          <t>25819</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>33439</t>
+          <t>33107</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51836</t>
+          <t>50862</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34898</t>
+          <t>35064</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49678</t>
+          <t>49993</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38268</t>
+          <t>39072</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52272</t>
+          <t>52862</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>77727</t>
+          <t>77933</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>97708</t>
+          <t>97785</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,83%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11806</t>
+          <t>11377</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23837</t>
+          <t>22962</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>9876</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21113</t>
+          <t>21527</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24143</t>
+          <t>24618</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40594</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4462</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>587</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11822</t>
+          <t>11739</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14228</t>
+          <t>15001</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25689</t>
+          <t>25953</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>20268</t>
+          <t>20443</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>34363</t>
+          <t>35025</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22634</t>
+          <t>22523</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32978</t>
+          <t>33232</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24107</t>
+          <t>24930</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>36694</t>
+          <t>36854</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>50201</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>67131</t>
+          <t>66068</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>61,2%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17135</t>
+          <t>16590</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>14365</t>
+          <t>13698</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>14337</t>
+          <t>13689</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>28247</t>
+          <t>27121</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -4369,12 +4369,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11446</t>
+          <t>12494</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9772</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>19774</t>
+          <t>18890</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -4482,12 +4482,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19276</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>28594</t>
+          <t>27846</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>18102</t>
+          <t>17932</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>26162</t>
+          <t>26031</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>39926</t>
+          <t>39820</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>51847</t>
+          <t>52266</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,69%</t>
         </is>
       </c>
     </row>
@@ -4595,12 +4595,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>10058</t>
+          <t>10723</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4610,12 +4610,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>5251</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>14306</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9150</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2563</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>10747</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>16453</t>
+          <t>16110</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>42079</t>
+          <t>43926</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>63848</t>
+          <t>64660</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>53259</t>
+          <t>54222</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>75604</t>
+          <t>78196</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>103489</t>
+          <t>102451</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>134145</t>
+          <t>133960</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -5164,12 +5164,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>134757</t>
+          <t>134170</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>160392</t>
+          <t>158608</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>159609</t>
+          <t>158455</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>184914</t>
+          <t>185431</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>300520</t>
+          <t>299415</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>336280</t>
+          <t>338997</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,33%</t>
         </is>
       </c>
     </row>
@@ -5277,12 +5277,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>43508</t>
+          <t>44625</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>64642</t>
+          <t>64656</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>33390</t>
+          <t>34072</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>53053</t>
+          <t>53395</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>82880</t>
+          <t>83808</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>110734</t>
+          <t>112311</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general autopercibida en 2012 (tasa de respuesta: 90,72%)</t>
+          <t>Menores según su salud general autopercibida en 2012 (tasa de respuesta: 90,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>7636</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17581</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12824</t>
+          <t>12860</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14284</t>
+          <t>14365</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26484</t>
+          <t>26982</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,6%</t>
         </is>
       </c>
     </row>
@@ -6080,12 +6080,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>12357</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22813</t>
+          <t>22947</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>10524</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18991</t>
+          <t>19195</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25952</t>
+          <t>25966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38707</t>
+          <t>40259</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>59,09%</t>
         </is>
       </c>
     </row>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9969</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4804</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>12574</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19582</t>
+          <t>19549</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2696</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>12166</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>8621</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17526</t>
+          <t>17007</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14169</t>
+          <t>14657</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22971</t>
+          <t>23530</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14842</t>
+          <t>14832</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24559</t>
+          <t>23890</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6812,12 +6812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32849</t>
+          <t>31651</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45725</t>
+          <t>44644</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>69,64%</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15607</t>
+          <t>15489</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>8355</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18587</t>
+          <t>18899</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2933</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15283</t>
+          <t>15029</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>9135</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>10093</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16375</t>
+          <t>16097</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26770</t>
+          <t>26807</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13884</t>
+          <t>13430</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21826</t>
+          <t>21285</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33252</t>
+          <t>32651</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46841</t>
+          <t>46767</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,77%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15054</t>
+          <t>14631</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2372</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8785</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>9846</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21007</t>
+          <t>21043</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>901</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7094</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>9916</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14069</t>
+          <t>14528</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>11980</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24133</t>
+          <t>24829</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18140</t>
+          <t>18053</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>32714</t>
+          <t>32074</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>33711</t>
+          <t>33065</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>52081</t>
+          <t>51004</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42846</t>
+          <t>42997</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56798</t>
+          <t>57612</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39088</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55114</t>
+          <t>55582</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>85143</t>
+          <t>86604</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>107189</t>
+          <t>106723</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>60,99%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>13688</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12753</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24782</t>
+          <t>24467</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>19572</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35769</t>
+          <t>34543</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11928</t>
+          <t>11692</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23541</t>
+          <t>23412</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>11885</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23981</t>
+          <t>24286</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>26414</t>
+          <t>27108</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>43804</t>
+          <t>44766</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>33,45%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>30378</t>
+          <t>30273</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43433</t>
+          <t>43793</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>26250</t>
+          <t>26292</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>39787</t>
+          <t>39704</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>59807</t>
+          <t>60593</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>80083</t>
+          <t>80512</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,15%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17451</t>
+          <t>17798</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>18092</t>
+          <t>18165</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>17574</t>
+          <t>18043</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>32228</t>
+          <t>32993</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>566</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>6907</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10387</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>11198</t>
+          <t>11885</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>8549</t>
+          <t>8498</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>19729</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7916</t>
+          <t>8196</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>15512</t>
+          <t>15330</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>14461</t>
+          <t>14660</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>24198</t>
+          <t>24607</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24801</t>
+          <t>25011</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>37101</t>
+          <t>36929</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,43%</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>11832</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>13358</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>4192</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>14031</t>
+          <t>13460</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>16423</t>
+          <t>15924</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>11678</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>25415</t>
+          <t>25732</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>60325</t>
+          <t>58232</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>83047</t>
+          <t>83591</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>55534</t>
+          <t>56512</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>79356</t>
+          <t>80118</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>120053</t>
+          <t>121677</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>152885</t>
+          <t>154300</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>145147</t>
+          <t>142685</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>171695</t>
+          <t>171609</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>137912</t>
+          <t>138395</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>164720</t>
+          <t>165444</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>291376</t>
+          <t>289985</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>330149</t>
+          <t>328049</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,69%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>30975</t>
+          <t>30626</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>49501</t>
+          <t>48505</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>51243</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>73207</t>
+          <t>73618</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>86731</t>
+          <t>86639</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>115190</t>
+          <t>117339</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -10554,7 +10554,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general autopercibida en 2016 (tasa de respuesta: 89,47%)</t>
+          <t>Menores según su salud general autopercibida en 2016 (tasa de respuesta: 89,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>3496</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10937,7 +10937,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -10975,12 +10975,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>538</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10990,12 +10990,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11010,12 +11010,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10976</t>
+          <t>11198</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11025,12 +11025,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13698</t>
+          <t>13822</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -11088,12 +11088,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>15265</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24298</t>
+          <t>23832</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11123,12 +11123,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>9165</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18983</t>
+          <t>18769</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11158,12 +11158,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27461</t>
+          <t>26451</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41153</t>
+          <t>40321</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>60,23%</t>
         </is>
       </c>
     </row>
@@ -11201,12 +11201,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14574</t>
+          <t>14132</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11216,12 +11216,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11236,12 +11236,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18195</t>
+          <t>18696</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11251,12 +11251,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11271,12 +11271,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16819</t>
+          <t>17196</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29643</t>
+          <t>29833</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11286,12 +11286,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11619,7 +11619,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2759</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>11181</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11672,12 +11672,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11692,12 +11692,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12259</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19717</t>
+          <t>20152</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -11770,12 +11770,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18225</t>
+          <t>18288</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29720</t>
+          <t>29925</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11785,12 +11785,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11805,12 +11805,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13827</t>
+          <t>14024</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24746</t>
+          <t>25161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35703</t>
+          <t>35773</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52010</t>
+          <t>51337</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,25%</t>
         </is>
       </c>
     </row>
@@ -11883,12 +11883,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10049</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20824</t>
+          <t>21394</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11898,12 +11898,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11918,12 +11918,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12764</t>
+          <t>12726</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23997</t>
+          <t>23450</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25929</t>
+          <t>26725</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41102</t>
+          <t>41277</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>718</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6165</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12354,12 +12354,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12374,12 +12374,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10896</t>
+          <t>11121</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>4741</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14702</t>
+          <t>14410</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -12452,12 +12452,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8088</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16066</t>
+          <t>16273</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9587</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19119</t>
+          <t>19076</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12522,12 +12522,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19945</t>
+          <t>20196</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32787</t>
+          <t>33171</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12537,12 +12537,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>54,38%</t>
         </is>
       </c>
     </row>
@@ -12565,12 +12565,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13608</t>
+          <t>13098</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>10437</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20475</t>
+          <t>20383</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12635,12 +12635,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18176</t>
+          <t>18652</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30767</t>
+          <t>31704</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12650,12 +12650,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>51,98%</t>
         </is>
       </c>
     </row>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12870,7 +12870,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12885,7 +12885,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -12908,12 +12908,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>613</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5736</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12978,12 +12978,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10299</t>
+          <t>9548</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -13021,12 +13021,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>12330</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25166</t>
+          <t>25238</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13036,12 +13036,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22938</t>
+          <t>22104</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13091,12 +13091,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25686</t>
+          <t>25004</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43013</t>
+          <t>42959</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13106,12 +13106,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -13134,12 +13134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>45625</t>
+          <t>45829</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61553</t>
+          <t>62538</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13169,12 +13169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31404</t>
+          <t>30377</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47399</t>
+          <t>46067</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13184,12 +13184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13204,12 +13204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>81431</t>
+          <t>79999</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>103996</t>
+          <t>103871</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13219,12 +13219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,7%</t>
         </is>
       </c>
     </row>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23427</t>
+          <t>23075</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>38609</t>
+          <t>38377</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13262,12 +13262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13282,12 +13282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>24851</t>
+          <t>24692</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>39724</t>
+          <t>39117</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13297,12 +13297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>51847</t>
+          <t>51603</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>73483</t>
+          <t>74235</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13332,12 +13332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,37%</t>
         </is>
       </c>
     </row>
@@ -13595,7 +13595,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13680,7 +13680,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -13703,12 +13703,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18309</t>
+          <t>18535</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13718,12 +13718,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13738,12 +13738,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6252</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>17065</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13753,12 +13753,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13773,12 +13773,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15914</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>30188</t>
+          <t>31564</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -13816,12 +13816,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>27698</t>
+          <t>27497</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40956</t>
+          <t>41024</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13831,12 +13831,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13851,12 +13851,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>23364</t>
+          <t>23514</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>37713</t>
+          <t>37355</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13866,12 +13866,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13886,12 +13886,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>55232</t>
+          <t>54501</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>74297</t>
+          <t>73859</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -13929,12 +13929,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>15581</t>
+          <t>15855</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>28529</t>
+          <t>28228</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13944,12 +13944,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13964,12 +13964,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20722</t>
+          <t>20024</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>34597</t>
+          <t>34407</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13979,12 +13979,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13999,12 +13999,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>39871</t>
+          <t>39678</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>59838</t>
+          <t>57745</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>42,08%</t>
         </is>
       </c>
     </row>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2384</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>10654</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14400,12 +14400,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14420,12 +14420,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>703</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14435,12 +14435,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14455,12 +14455,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>13759</t>
+          <t>15154</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>23,1%</t>
         </is>
       </c>
     </row>
@@ -14498,12 +14498,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14174</t>
+          <t>14389</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14513,12 +14513,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14533,12 +14533,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10783</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>20429</t>
+          <t>21224</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14548,12 +14548,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14568,12 +14568,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>18674</t>
+          <t>19041</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>32614</t>
+          <t>31791</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14583,12 +14583,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>48,46%</t>
         </is>
       </c>
     </row>
@@ -14611,12 +14611,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>11406</t>
+          <t>11237</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>20467</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14626,12 +14626,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14646,12 +14646,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>11614</t>
+          <t>11548</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>21793</t>
+          <t>21180</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14661,12 +14661,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14681,12 +14681,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>25205</t>
+          <t>24757</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>38686</t>
+          <t>38949</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14696,12 +14696,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>59,37%</t>
         </is>
       </c>
     </row>
@@ -14846,7 +14846,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14861,7 +14861,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14911,12 +14911,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5470</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14954,12 +14954,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14969,12 +14969,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14989,12 +14989,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10212</t>
+          <t>9916</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15004,12 +15004,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15024,12 +15024,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>14983</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15039,12 +15039,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -15067,12 +15067,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>36905</t>
+          <t>36837</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>57302</t>
+          <t>56977</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15082,12 +15082,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15102,12 +15102,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>39077</t>
+          <t>38996</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>60814</t>
+          <t>61223</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15117,12 +15117,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15137,12 +15137,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>81157</t>
+          <t>81351</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>113293</t>
+          <t>111962</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15152,12 +15152,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -15180,12 +15180,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>139519</t>
+          <t>139295</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>169110</t>
+          <t>168472</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15195,12 +15195,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15215,12 +15215,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>117256</t>
+          <t>117027</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>145374</t>
+          <t>146004</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15230,12 +15230,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15250,12 +15250,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>264717</t>
+          <t>266167</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>306350</t>
+          <t>307139</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15265,12 +15265,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,9%</t>
         </is>
       </c>
     </row>
@@ -15293,12 +15293,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>87567</t>
+          <t>88377</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>117004</t>
+          <t>115517</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15308,12 +15308,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15328,12 +15328,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>107760</t>
+          <t>108945</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>137151</t>
+          <t>137192</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15343,12 +15343,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15363,12 +15363,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>204196</t>
+          <t>204928</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>243252</t>
+          <t>243332</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15378,12 +15378,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -15562,7 +15562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general autopercibida en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según su salud general autopercibida en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -15983,12 +15983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10578</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -15998,12 +15998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -16018,12 +16018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9834</t>
+          <t>10008</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20466</t>
+          <t>20689</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -16053,12 +16053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15511</t>
+          <t>14677</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28036</t>
+          <t>28337</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -16096,12 +16096,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>10156</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19943</t>
+          <t>19466</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -16111,12 +16111,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -16131,12 +16131,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>12543</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23558</t>
+          <t>23609</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -16146,12 +16146,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -16166,12 +16166,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26884</t>
+          <t>26201</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40046</t>
+          <t>40265</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,84%</t>
         </is>
       </c>
     </row>
@@ -16209,12 +16209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13242</t>
+          <t>13772</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -16244,12 +16244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -16259,12 +16259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -16279,12 +16279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21792</t>
+          <t>21491</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -16557,7 +16557,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -16572,7 +16572,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -16627,7 +16627,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -16642,7 +16642,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -16665,12 +16665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16456</t>
+          <t>16669</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -16680,12 +16680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -16700,12 +16700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15889</t>
+          <t>16385</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -16715,12 +16715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -16735,12 +16735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16817</t>
+          <t>16654</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30535</t>
+          <t>29939</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>48,6%</t>
         </is>
       </c>
     </row>
@@ -16778,12 +16778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16967</t>
+          <t>17199</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -16793,12 +16793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -16813,12 +16813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11663</t>
+          <t>11313</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21553</t>
+          <t>21843</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -16828,12 +16828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -16848,12 +16848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22200</t>
+          <t>22411</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36194</t>
+          <t>36065</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -16863,12 +16863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,54%</t>
         </is>
       </c>
     </row>
@@ -16891,12 +16891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -16906,12 +16906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -16926,12 +16926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9623</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -16941,12 +16941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -16961,12 +16961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13894</t>
+          <t>13705</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -16976,12 +16976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -17289,7 +17289,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -17309,7 +17309,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -17347,12 +17347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9969</t>
+          <t>10229</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -17362,12 +17362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -17382,12 +17382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12079</t>
+          <t>12720</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -17397,12 +17397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -17417,12 +17417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>20430</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -17432,12 +17432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>48,37%</t>
         </is>
       </c>
     </row>
@@ -17460,12 +17460,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8575</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -17475,12 +17475,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -17495,12 +17495,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>10590</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20225</t>
+          <t>20423</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -17510,12 +17510,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -17530,12 +17530,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15001</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26784</t>
+          <t>27093</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -17545,12 +17545,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>64,15%</t>
         </is>
       </c>
     </row>
@@ -17573,12 +17573,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -17588,12 +17588,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -17608,12 +17608,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>929</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7857</t>
+          <t>7879</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -17623,12 +17623,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -17643,12 +17643,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10289</t>
+          <t>10944</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -17658,12 +17658,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -17921,7 +17921,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -17936,7 +17936,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -17991,7 +17991,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -18006,7 +18006,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -18029,12 +18029,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22090</t>
+          <t>21378</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -18064,12 +18064,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17632</t>
+          <t>17100</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37468</t>
+          <t>37321</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -18079,12 +18079,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20311</t>
+          <t>19117</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>52267</t>
+          <t>52982</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -18114,12 +18114,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,94%</t>
         </is>
       </c>
     </row>
@@ -18142,12 +18142,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41863</t>
+          <t>41104</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -18157,12 +18157,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -18177,12 +18177,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17867</t>
+          <t>18574</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38487</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -18192,12 +18192,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -18212,12 +18212,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26756</t>
+          <t>26283</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>68271</t>
+          <t>69076</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -18227,12 +18227,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>49,47%</t>
         </is>
       </c>
     </row>
@@ -18255,12 +18255,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>8012</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55910</t>
+          <t>55998</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -18270,12 +18270,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -18290,12 +18290,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9755</t>
+          <t>9775</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29952</t>
+          <t>31266</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -18305,12 +18305,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -18325,12 +18325,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24957</t>
+          <t>24260</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>93930</t>
+          <t>92988</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -18340,12 +18340,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>66,59%</t>
         </is>
       </c>
     </row>
@@ -18603,7 +18603,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -18618,7 +18618,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -18673,7 +18673,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -18688,7 +18688,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15838</t>
+          <t>16333</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -18726,12 +18726,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -18746,12 +18746,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>23416</t>
+          <t>23478</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45399</t>
+          <t>47231</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -18761,12 +18761,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -18781,12 +18781,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>34482</t>
+          <t>33379</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>61857</t>
+          <t>60575</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -18796,12 +18796,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>62,78%</t>
         </is>
       </c>
     </row>
@@ -18824,12 +18824,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>11374</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21049</t>
+          <t>21417</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -18839,12 +18839,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>10698</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>31753</t>
+          <t>31900</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -18874,12 +18874,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -18894,12 +18894,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>26726</t>
+          <t>25850</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>49342</t>
+          <t>49652</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -18909,12 +18909,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,46%</t>
         </is>
       </c>
     </row>
@@ -18937,12 +18937,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>11917</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -18952,12 +18952,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -18972,12 +18972,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>10567</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -18987,12 +18987,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -19007,12 +19007,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6697</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>19343</t>
+          <t>19480</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -19315,12 +19315,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>859</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6750</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -19330,12 +19330,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -19350,12 +19350,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>870</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -19365,12 +19365,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -19393,12 +19393,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12997</t>
+          <t>12700</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -19408,12 +19408,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -19428,12 +19428,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>14088</t>
+          <t>14191</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -19443,12 +19443,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -19463,12 +19463,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>23761</t>
+          <t>24341</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -19506,12 +19506,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>15380</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>23662</t>
+          <t>23928</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -19521,12 +19521,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -19541,12 +19541,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>15252</t>
+          <t>14867</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>25977</t>
+          <t>25491</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -19556,12 +19556,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -19576,12 +19576,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>32627</t>
+          <t>32551</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>46423</t>
+          <t>46519</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -19591,12 +19591,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,22%</t>
         </is>
       </c>
     </row>
@@ -19619,12 +19619,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>518</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -19634,12 +19634,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -19654,12 +19654,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -19669,12 +19669,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -19689,12 +19689,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>11626</t>
+          <t>12046</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -19704,12 +19704,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -19962,12 +19962,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>675</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -19977,7 +19977,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -19997,12 +19997,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -20012,12 +20012,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -20032,12 +20032,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>12651</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -20047,12 +20047,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -20075,12 +20075,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>34823</t>
+          <t>34891</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>68914</t>
+          <t>69450</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -20090,12 +20090,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -20110,12 +20110,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>84523</t>
+          <t>86328</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>126406</t>
+          <t>124552</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -20125,12 +20125,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -20145,12 +20145,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>130130</t>
+          <t>127002</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>188802</t>
+          <t>184719</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -20160,12 +20160,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>38,82%</t>
         </is>
       </c>
     </row>
@@ -20188,12 +20188,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>57567</t>
+          <t>59019</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>110397</t>
+          <t>110955</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -20203,12 +20203,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -20223,12 +20223,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>100346</t>
+          <t>101430</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>138013</t>
+          <t>138306</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -20238,12 +20238,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -20258,12 +20258,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>174694</t>
+          <t>172520</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>239677</t>
+          <t>239241</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -20273,12 +20273,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,28%</t>
         </is>
       </c>
     </row>
@@ -20301,12 +20301,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>32496</t>
+          <t>31298</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>119944</t>
+          <t>106216</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -20336,12 +20336,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>31069</t>
+          <t>30231</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>60919</t>
+          <t>58803</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -20351,12 +20351,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -20371,12 +20371,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>69948</t>
+          <t>70044</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>169044</t>
+          <t>177420</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -20386,12 +20386,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>37,29%</t>
         </is>
       </c>
     </row>
